--- a/assets/constructions/examples/ctd_collet_spring.xlsx
+++ b/assets/constructions/examples/ctd_collet_spring.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T6"/>
+  <dimension ref="A1:X6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -529,23 +529,51 @@
           <t>releasepack</t>
         </is>
       </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CER16080</t>
+          <t>ER25-8UP</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>LIKON</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
+          <t>DEREK</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Цанги ER</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>34</v>
+      </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
+      <c r="G2" t="n">
+        <v>26</v>
+      </c>
       <c r="H2" t="inlineStr">
         <is>
           <t>HA-7/8</t>
@@ -558,7 +586,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>LIKON</t>
+          <t>DEREK</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -570,13 +598,15 @@
       <c r="M2" t="b">
         <v>0</v>
       </c>
-      <c r="N2" t="inlineStr"/>
+      <c r="N2" t="n">
+        <v>0.005</v>
+      </c>
       <c r="O2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>ER16</t>
+          <t>ER25</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr"/>
@@ -586,65 +616,71 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2022/LIKON Инструментальный каталог</t>
-        </is>
+          <t>2019/DEREK Металлорежущий инструмент и оснастка</t>
+        </is>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V2" t="n">
+        <v>20.29</v>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="X2" t="n">
+        <v>1663.25</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>DSK20-14</t>
+          <t>CER11010AA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>DEREK</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Цанги DSK</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>50</v>
-      </c>
+          <t>LIKON</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
-      <c r="G3" t="n">
-        <v>24</v>
-      </c>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>HA-13.5/14</t>
+          <t>HA-1</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>HA-13.5..14</t>
+          <t>HA-1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>DEREK</t>
+          <t>LIKON</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>13.5</v>
+        <v>1</v>
       </c>
       <c r="L3" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="M3" t="b">
         <v>0</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>DER_DSK_COLLET:20</t>
+          <t>ER11</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr"/>
@@ -654,127 +690,153 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2019/DEREK Металлорежущий инструмент и оснастка</t>
-        </is>
-      </c>
+          <t>2022/LIKON Инструментальный каталог</t>
+        </is>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
+      </c>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>G020-UP-16x2</t>
+          <t>ER40-12</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>KFH</t>
+          <t>AMATI</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Цанги ER</t>
+          <t>ER</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="n">
-        <v>17</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>HA-2</t>
-        </is>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>HA-2</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>KFH</t>
-        </is>
-      </c>
+          <t>HA-11..12</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="L4" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="M4" t="b">
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>0.006</v>
+        <v>0.005</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>ER16</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr"/>
+          <t>ER40</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>DIN 6499</t>
+        </is>
+      </c>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>KFH Общий каталог 2011</t>
-        </is>
+          <t>2025 / AMATI Инструментальная и технологическая оснастка</t>
+        </is>
+      </c>
+      <c r="U4" t="n">
+        <v>1</v>
+      </c>
+      <c r="V4" t="n">
+        <v>92.40000000000001</v>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="X4" t="n">
+        <v>1134.73</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CER40060</t>
+          <t>ER25-12A</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>LIKON</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
+          <t>DEREK</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Цанги ER</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>34</v>
+      </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
+      <c r="G5" t="n">
+        <v>26</v>
+      </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>HA-5/6</t>
+          <t>HA-11/12</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>HA-5..6</t>
+          <t>HA-11..12</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>LIKON</t>
+          <t>DEREK</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="L5" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M5" t="b">
         <v>0</v>
       </c>
-      <c r="N5" t="inlineStr"/>
+      <c r="N5" t="n">
+        <v>0.01</v>
+      </c>
       <c r="O5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>ER40</t>
+          <t>ER25</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr"/>
@@ -784,68 +846,102 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2022/LIKON Инструментальный каталог</t>
-        </is>
+          <t>2019/DEREK Металлорежущий инструмент и оснастка</t>
+        </is>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
+      </c>
+      <c r="V5" t="n">
+        <v>10.94</v>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="X5" t="n">
+        <v>896.79</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CER40080AA</t>
+          <t>ER50-30</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>LIKON</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
+          <t>AMATI</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>ER</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>60</v>
+      </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>HA-8</t>
-        </is>
-      </c>
+      <c r="G6" t="n">
+        <v>50</v>
+      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>HA-8</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>LIKON</t>
-        </is>
-      </c>
+          <t>HA-28..30</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="n">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="L6" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="M6" t="b">
         <v>0</v>
       </c>
-      <c r="N6" t="inlineStr"/>
+      <c r="N6" t="n">
+        <v>0.005</v>
+      </c>
       <c r="O6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>ER40</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr"/>
+          <t>ER50</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>DIN 6499</t>
+        </is>
+      </c>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2022/LIKON Инструментальный каталог</t>
-        </is>
+          <t>2025 / AMATI Инструментальная и технологическая оснастка</t>
+        </is>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
+      </c>
+      <c r="V6" t="n">
+        <v>207.9</v>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="X6" t="n">
+        <v>2553.14</v>
       </c>
     </row>
   </sheetData>
